--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7246376811594203</v>
+        <v>0.8924731182795699</v>
       </c>
       <c r="B2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6971830985915493</v>
+        <v>0.7323943661971831</v>
       </c>
       <c r="D2">
-        <v>0.4574468085106383</v>
+        <v>0.3140495867768595</v>
       </c>
       <c r="E2">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8924731182795699</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7323943661971831</v>
+        <v>0.7183098591549296</v>
       </c>
       <c r="D2">
-        <v>0.3140495867768595</v>
+        <v>0.3174603174603174</v>
       </c>
       <c r="E2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
